--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK12"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45901.60416666666</v>
+        <v>45901.66666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45901.66666666666</v>
+        <v>45901.79166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1651,394 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45901.6875</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Chapecoense</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>45901.79166666666</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>21:15</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Ferro Carril Oeste</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Racing Córdoba</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="3" t="n">
         <v>45901.88541666666</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="3" t="n">
-        <v>45901.91666666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK9"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,16 +1218,16 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45901.66666666666</v>
+        <v>45901.60416666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45901.66666666666</v>
+        <v>45901.625</v>
       </c>
     </row>
     <row r="8">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45901.79166666666</v>
+        <v>45901.625</v>
       </c>
     </row>
     <row r="9">
@@ -1531,127 +1531,772 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Nuova Monterosi</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pineto</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="3" t="n">
+        <v>45901.66666666666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HFX Wanderers FC</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>York9 FC</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>45901.66666666666</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Leganés</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruña</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="3" t="n">
+        <v>45901.6875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="3" t="n">
+        <v>45901.79166666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>21:15</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Argentina Prim B Nacional</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Ferro Carril Oeste</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Racing Córdoba</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="3" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3" t="n">
         <v>45901.88541666666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <v>45901.91666666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK14"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>3.36</v>
       </c>
       <c r="N5" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45901.66666666666</v>
+        <v>45901.625</v>
       </c>
     </row>
     <row r="10">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45901.6875</v>
+        <v>45901.66666666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45901.79166666666</v>
+        <v>45901.6875</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45901.88541666666</v>
+        <v>45901.79166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,126 +2176,255 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ferro Carril Oeste</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Racing Córdoba</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <v>45901.88541666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Bay</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
+      <c r="L15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
         <v>45901.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>4.42</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="M5" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>4.42</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1089,16 +1089,16 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,16 +1218,16 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>4.42</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>4.42</v>
+        <v>5.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>4.42</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1959,43 +1959,43 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.17</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>3.94</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y12" t="n">
         <v>2.3</v>
@@ -2004,16 +2004,16 @@
         <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>2.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,16 +1218,16 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK15"/>
+  <dimension ref="A1:AK13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.36</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45901.625</v>
+        <v>45901.66666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45901.625</v>
+        <v>45901.66666666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45901.66666666666</v>
+        <v>45901.6875</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="N11" t="n">
-        <v>3.04</v>
+        <v>3.71</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45901.66666666666</v>
+        <v>45901.79166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>3.17</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.94</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="X12" t="n">
-        <v>2.9</v>
+        <v>2.22</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45901.6875</v>
+        <v>45901.88541666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="M13" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.71</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,16 +2121,16 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2167,264 +2167,6 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45901.79166666666</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>21:15</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Ferro Carril Oeste</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Racing Córdoba</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
-        <v>45901.88541666666</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
         <v>45901.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1185,37 +1185,37 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
         <v>1.5</v>
@@ -1230,16 +1230,16 @@
         <v>1.53</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1701,43 +1701,43 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.94</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>2.3</v>
@@ -1746,16 +1746,16 @@
         <v>1.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>3.36</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1701,43 +1701,43 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.17</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>3.94</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y10" t="n">
         <v>2.3</v>
@@ -1746,16 +1746,16 @@
         <v>1.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45901.54166666666</v>
+        <v>45901.5</v>
       </c>
     </row>
     <row r="3">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45901.58333333334</v>
+        <v>45901.54166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.59</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>2.93</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45901.60416666666</v>
+        <v>45901.58333333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="M7" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45901.625</v>
+        <v>45901.60416666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="N8" t="n">
-        <v>2.63</v>
+        <v>3.21</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45901.66666666666</v>
+        <v>45901.625</v>
       </c>
     </row>
     <row r="9">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>3.94</v>
+        <v>2.63</v>
       </c>
       <c r="O10" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45901.6875</v>
+        <v>45901.66666666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45901.79166666666</v>
+        <v>45901.6875</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>3.71</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,16 +1992,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="X12" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45901.88541666666</v>
+        <v>45901.79166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
         <v>3.35</v>
@@ -2121,52 +2121,181 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3" t="n">
+        <v>45901.88541666666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.86</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="Z14" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="3" t="n">
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
         <v>45901.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK14"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.47</v>
+        <v>3.31</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="N2" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>3.36</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1089,16 +1089,16 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>3.04</v>
+        <v>2.63</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.63</v>
+        <v>3.04</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>3.03</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,16 +2121,16 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45901.88541666666</v>
+        <v>45901.83333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
         <v>3.35</v>
@@ -2250,52 +2250,181 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <v>45901.88541666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.86</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="Z15" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
         <v>45901.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK15"/>
+  <dimension ref="A1:AK18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
         <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X6" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45901.60416666666</v>
+        <v>45901.58333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45901.625</v>
+        <v>45901.60416666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45901.66666666666</v>
+        <v>45901.625</v>
       </c>
     </row>
     <row r="10">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="N10" t="n">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45901.66666666666</v>
+        <v>45901.625</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45901.6875</v>
+        <v>45901.625</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="M12" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>3.71</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,16 +1992,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45901.79166666666</v>
+        <v>45901.66666666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="M13" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45901.83333333334</v>
+        <v>45901.66666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45901.88541666666</v>
+        <v>45901.6875</v>
       </c>
     </row>
     <row r="15">
@@ -2305,126 +2305,513 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
+        <v>45901.79166666666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="3" t="n">
+        <v>45901.83333333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ferro Carril Oeste</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Racing Córdoba</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>45901.88541666666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Bay</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="L18" t="n">
         <v>1.94</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M18" t="n">
         <v>3.3</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N18" t="n">
         <v>3.35</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.86</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z18" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
         <v>45901.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>3.94</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y17" t="n">
         <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.31</v>
+        <v>2.96</v>
       </c>
       <c r="M2" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>3.36</v>
       </c>
       <c r="N7" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>2.59</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>2.93</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2604,43 +2604,43 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>3.94</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>2.3</v>
@@ -2649,16 +2649,16 @@
         <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1701,43 +1701,43 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Y10" t="n">
         <v>2.5</v>
@@ -1746,16 +1746,16 @@
         <v>1.53</v>
       </c>
       <c r="AA10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
         <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>3.94</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
         <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="M6" t="n">
-        <v>2.86</v>
+        <v>3.36</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
-        <v>2.3</v>
+        <v>2.79</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
-        <v>3.36</v>
+        <v>2.86</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X8" t="n">
         <v>2.3</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.79</v>
-      </c>
       <c r="Y8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>2.59</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="M6" t="n">
-        <v>3.36</v>
+        <v>2.86</v>
       </c>
       <c r="N6" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X6" t="n">
         <v>2.3</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.79</v>
-      </c>
       <c r="Y6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
         <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.94</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2871,28 +2871,28 @@
         <v>3.71</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
         <v>1.55</v>
@@ -2907,16 +2907,16 @@
         <v>1.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3387,34 +3387,34 @@
         <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y23" t="n">
         <v>1.88</v>
@@ -3423,16 +3423,16 @@
         <v>1.82</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="M6" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X6" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3000,34 +3000,34 @@
         <v>3.03</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y20" t="n">
         <v>2.35</v>
@@ -3036,16 +3036,16 @@
         <v>1.53</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3129,28 +3129,28 @@
         <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W21" t="n">
         <v>1.62</v>
@@ -3159,22 +3159,22 @@
         <v>2.15</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.96</v>
+        <v>3.31</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="N2" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="O2" t="n">
         <v>4</v>
@@ -684,13 +684,13 @@
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="R2" t="n">
         <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="T2" t="n">
         <v>3.1</v>
@@ -699,31 +699,31 @@
         <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,62 +1314,62 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.56</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
       <c r="AE7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1980,13 +1980,13 @@
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
         <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V12" t="n">
         <v>1.03</v>
@@ -2007,7 +2007,7 @@
         <v>3.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AC12" t="n">
         <v>1.91</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2484,52 +2484,52 @@
         <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2874,7 +2874,7 @@
         <v>2.65</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
         <v>4.75</v>
@@ -2886,7 +2886,7 @@
         <v>2.34</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
         <v>1.22</v>
@@ -2916,7 +2916,7 @@
         <v>2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="M21" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -3141,7 +3141,7 @@
         <v>1.65</v>
       </c>
       <c r="S21" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="T21" t="n">
         <v>3.96</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
         <v>3.22</v>
@@ -3448,7 +3448,7 @@
         <v>1.24</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1572,43 +1572,43 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Y9" t="n">
         <v>2.5</v>
@@ -1617,16 +1617,16 @@
         <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,62 +1443,62 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.56</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,43 +1572,43 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
         <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Y9" t="n">
         <v>2.5</v>
@@ -1617,16 +1617,16 @@
         <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
         <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,62 +1185,62 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.56</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
       <c r="AE6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,43 +1572,43 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Y9" t="n">
         <v>2.5</v>
@@ -1617,16 +1617,16 @@
         <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>2.59</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>2.93</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>2.15</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AA21" t="n">
         <v>6.16</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.31</v>
+        <v>3.47</v>
       </c>
       <c r="M2" t="n">
-        <v>2.98</v>
+        <v>3.22</v>
       </c>
       <c r="N2" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="O2" t="n">
         <v>4</v>
@@ -684,46 +684,46 @@
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="R2" t="n">
         <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X2" t="n">
-        <v>2.67</v>
+        <v>2.95</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AA2" t="n">
         <v>4.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>18.68</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="M9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O9" t="n">
         <v>3.3</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>2.76</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.59</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2355,52 +2355,52 @@
         <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
         <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
         <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X15" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="AB15" t="n">
         <v>1.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>3.84</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Z17" t="n">
         <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18.68</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>8.08</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>18.68</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1314,46 +1314,46 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="M7" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="P7" t="n">
         <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="R7" t="n">
         <v>1.63</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
         <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Z7" t="n">
         <v>1.4</v>
@@ -1362,13 +1362,13 @@
         <v>5.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
         <v>1.65</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="M19" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.71</v>
+        <v>3.84</v>
       </c>
       <c r="O19" t="n">
         <v>2.65</v>
@@ -2880,43 +2880,43 @@
         <v>4.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="S19" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
         <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
         <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.17</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.22</v>
+        <v>4.28</v>
       </c>
       <c r="R20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.5</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AA20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="M21" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
         <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="S21" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T21" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="U21" t="n">
         <v>1.19</v>
       </c>
       <c r="V21" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="W21" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.16</v>
+        <v>6.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC21" t="n">
         <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="N22" t="n">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3378,55 +3378,55 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="O23" t="n">
-        <v>2.57</v>
+        <v>2.36</v>
       </c>
       <c r="P23" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
         <v>4.45</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T23" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X23" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
         <v>3.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC23" t="n">
         <v>1.74</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
         <v>1.83</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>8.08</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>18.68</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>18.68</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.56</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1704,7 +1704,7 @@
         <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="N10" t="n">
         <v>3.5</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="M11" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="N11" t="n">
-        <v>4.12</v>
+        <v>3.88</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2736,10 +2736,10 @@
         <v>2.62</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2874,16 +2874,16 @@
         <v>2.65</v>
       </c>
       <c r="P19" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
         <v>4.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T19" t="n">
         <v>3.3</v>
@@ -2892,7 +2892,7 @@
         <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W19" t="n">
         <v>1.44</v>
@@ -2901,7 +2901,7 @@
         <v>2.44</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Z19" t="n">
         <v>1.52</v>
@@ -2916,7 +2916,7 @@
         <v>2.23</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3000,52 +3000,52 @@
         <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="T20" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V20" t="n">
         <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X20" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="Y20" t="n">
         <v>2.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="N22" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.47</v>
+        <v>2.98</v>
       </c>
       <c r="M2" t="n">
-        <v>3.22</v>
+        <v>3.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P2" t="n">
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="R2" t="n">
         <v>1.48</v>
@@ -693,37 +693,37 @@
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
         <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>2.95</v>
+        <v>2.67</v>
       </c>
       <c r="Y2" t="n">
         <v>2.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>18.68</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>8.08</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>18.68</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="M10" t="n">
-        <v>3.11</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1743,7 +1743,7 @@
         <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="M11" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.88</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2094,7 +2094,7 @@
         <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
         <v>2.73</v>
@@ -2103,13 +2103,13 @@
         <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.38</v>
+        <v>3.97</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
         <v>3</v>
@@ -2127,22 +2127,22 @@
         <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
         <v>1.67</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2880,10 +2880,10 @@
         <v>4.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
         <v>3.3</v>
@@ -2892,31 +2892,31 @@
         <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="W19" t="n">
         <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Z19" t="n">
         <v>1.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3378,22 +3378,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="M23" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="O23" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="P23" t="n">
         <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.45</v>
+        <v>4.68</v>
       </c>
       <c r="R23" t="n">
         <v>1.35</v>
@@ -3402,22 +3402,22 @@
         <v>2.85</v>
       </c>
       <c r="T23" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V23" t="n">
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Z23" t="n">
         <v>1.85</v>
@@ -3429,10 +3429,10 @@
         <v>1.29</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
         <v>1.83</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18.68</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>8.08</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>18.68</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>4.42</v>
       </c>
       <c r="O7" t="n">
         <v>2.7</v>
@@ -1329,7 +1329,7 @@
         <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
         <v>1.63</v>
@@ -1338,10 +1338,10 @@
         <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
         <v>1.12</v>
@@ -1350,10 +1350,10 @@
         <v>1.56</v>
       </c>
       <c r="X7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Z7" t="n">
         <v>1.4</v>
@@ -1365,7 +1365,7 @@
         <v>1.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="AD7" t="n">
         <v>1.62</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>2.09</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>3.84</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3123,16 +3123,16 @@
         <v>2.33</v>
       </c>
       <c r="M21" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="N21" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Q21" t="n">
         <v>4</v>
@@ -3141,31 +3141,31 @@
         <v>1.57</v>
       </c>
       <c r="S21" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="U21" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V21" t="n">
         <v>1.14</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AB21" t="n">
         <v>1.11</v>
@@ -3174,7 +3174,7 @@
         <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
         <v>1.57</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK23"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>8.08</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>18.68</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>18.68</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45901.79166666666</v>
+        <v>45901.75</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,78 +2991,78 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.2</v>
       </c>
-      <c r="M20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AD20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.7</v>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45901.83333333334</v>
+        <v>45901.79166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45901.88541666666</v>
+        <v>45901.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,7 +3249,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
         <v>2.9</v>
@@ -3258,52 +3258,52 @@
         <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X22" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45901.89583333334</v>
+        <v>45901.83333333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,126 +3337,513 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ferro Carril Oeste</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Racing Córdoba</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>45901.88541666666</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Montego Bay United</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Treasure Beach</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45901.89583333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
+        <v>45901.89583333334</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Bay</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="L26" t="n">
         <v>1.77</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M26" t="n">
         <v>3.55</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N26" t="n">
         <v>3.95</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O26" t="n">
         <v>2.35</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P26" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q26" t="n">
         <v>4.68</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R26" t="n">
         <v>1.35</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S26" t="n">
         <v>2.85</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T26" t="n">
         <v>2.68</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U26" t="n">
         <v>1.39</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V26" t="n">
         <v>1.02</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W26" t="n">
         <v>1.25</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X26" t="n">
         <v>3.28</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Y26" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="Z26" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AA26" t="n">
         <v>3.04</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AB26" t="n">
         <v>1.29</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AC26" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AD26" t="n">
         <v>1.92</v>
       </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.18</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AH26" t="n">
         <v>1.83</v>
       </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="3" t="n">
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3" t="n">
         <v>45901.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18.68</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>8.08</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>18.68</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1446,10 +1446,10 @@
         <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="N8" t="n">
-        <v>4.42</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
         <v>2.7</v>
@@ -1458,19 +1458,19 @@
         <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="R8" t="n">
         <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="T8" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
         <v>1.12</v>
@@ -1479,19 +1479,19 @@
         <v>1.56</v>
       </c>
       <c r="X8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Y8" t="n">
         <v>2.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AA8" t="n">
         <v>5.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC8" t="n">
         <v>2.23</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.27</v>
+        <v>1.87</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.76</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.09</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.84</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
         <v>3</v>
@@ -3399,10 +3399,10 @@
         <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="T23" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="U23" t="n">
         <v>1.22</v>
@@ -3417,13 +3417,13 @@
         <v>2.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Z23" t="n">
         <v>1.36</v>
       </c>
       <c r="AA23" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AB23" t="n">
         <v>1.11</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH23" t="n">
         <v>1.57</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>8.08</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>18.68</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2358,16 +2358,16 @@
         <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q15" t="n">
         <v>3.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
         <v>3</v>
@@ -2382,7 +2382,7 @@
         <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="Y15" t="n">
         <v>2.1</v>
@@ -2397,10 +2397,10 @@
         <v>1.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
         <v>1.45</v>
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.17</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>3.84</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Z18" t="n">
         <v>1.62</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.56</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="O22" t="n">
         <v>2.91</v>
@@ -3264,46 +3264,46 @@
         <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.22</v>
+        <v>4.06</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>2.35</v>
@@ -3798,16 +3798,16 @@
         <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X26" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AA26" t="n">
         <v>3.04</v>
@@ -3816,10 +3816,10 @@
         <v>1.29</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="M2" t="n">
-        <v>3.09</v>
+        <v>3.22</v>
       </c>
       <c r="N2" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="O2" t="n">
         <v>3.7</v>
@@ -684,7 +684,7 @@
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="R2" t="n">
         <v>1.48</v>
@@ -693,7 +693,7 @@
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U2" t="n">
         <v>1.3</v>
@@ -702,25 +702,25 @@
         <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="X2" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="Y2" t="n">
         <v>2.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.01</v>
+        <v>4.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
         <v>1.8</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -801,10 +801,10 @@
         <v>1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>10.5</v>
+        <v>8.08</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>18.68</v>
       </c>
       <c r="O3" t="n">
         <v>1.36</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1065,52 +1065,52 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>3.67</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>2.33</v>
+        <v>2.69</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3.3</v>
       </c>
-      <c r="N10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.09</v>
+        <v>2.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.17</v>
+        <v>2.83</v>
       </c>
       <c r="N18" t="n">
-        <v>3.84</v>
+        <v>2.68</v>
       </c>
       <c r="O18" t="n">
-        <v>2.81</v>
+        <v>3.54</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3.46</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X18" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.09</v>
+        <v>4.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="N20" t="n">
-        <v>3.84</v>
+        <v>3.71</v>
       </c>
       <c r="O20" t="n">
         <v>2.65</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="Q20" t="n">
         <v>4.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="T20" t="n">
         <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AA20" t="n">
         <v>5.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="M23" t="n">
         <v>2.7</v>
@@ -3390,7 +3390,7 @@
         <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q23" t="n">
         <v>4</v>
@@ -3399,7 +3399,7 @@
         <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T23" t="n">
         <v>3.8</v>
@@ -3417,7 +3417,7 @@
         <v>2.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Z23" t="n">
         <v>1.36</v>
@@ -3426,13 +3426,13 @@
         <v>5.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
         <v>1.57</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.26</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="T4" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="U4" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,77 +1056,77 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.55</v>
+        <v>3.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="T5" t="n">
-        <v>2.79</v>
+        <v>3.15</v>
       </c>
       <c r="U5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.36</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.27</v>
-      </c>
       <c r="X5" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="Z5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.78</v>
       </c>
-      <c r="AA5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.26</v>
       </c>
-      <c r="AC5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1704,10 +1704,10 @@
         <v>2.65</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="O10" t="n">
         <v>3.65</v>
@@ -1716,25 +1716,25 @@
         <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S10" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="U10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
         <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="X10" t="n">
         <v>2.62</v>
@@ -1743,7 +1743,7 @@
         <v>2.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AA10" t="n">
         <v>4.25</v>
@@ -1755,7 +1755,7 @@
         <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="O11" t="n">
         <v>2.54</v>
@@ -1869,22 +1869,22 @@
         <v>2.69</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AA11" t="n">
         <v>4.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
         <v>1.8</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
         <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.93</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="N17" t="n">
-        <v>3.72</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>3.52</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.35</v>
+        <v>3.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X17" t="n">
-        <v>2.79</v>
+        <v>2.49</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.12</v>
+        <v>4.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,77 +2733,77 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="M18" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.68</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.54</v>
+        <v>2.91</v>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.46</v>
+        <v>4.15</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X18" t="n">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.65</v>
+        <v>4.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,28 +3249,28 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>2.91</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="T22" t="n">
         <v>3.34</v>
@@ -3282,28 +3282,28 @@
         <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="X22" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AB22" t="n">
         <v>1.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="O26" t="n">
         <v>2.35</v>
@@ -3783,7 +3783,7 @@
         <v>4.68</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
         <v>2.85</v>
@@ -3798,16 +3798,16 @@
         <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
         <v>3.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
         <v>3.04</v>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
         <v>1.83</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="M3" t="n">
-        <v>8.08</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>18.68</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.36</v>
       </c>
-      <c r="P3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>15</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.12</v>
-      </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.08</v>
+        <v>3.98</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.35</v>
+        <v>1.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>6.75</v>
+        <v>1.41</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>8.08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>18.68</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.16</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.43</v>
       </c>
-      <c r="S5" t="n">
+      <c r="Z5" t="n">
         <v>2.55</v>
       </c>
-      <c r="T5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AA5" t="n">
-        <v>3.98</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.88</v>
+        <v>3.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.41</v>
+        <v>6.75</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>2.33</v>
+        <v>2.69</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
         <v>3.65</v>
@@ -1740,10 +1740,10 @@
         <v>2.62</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
         <v>4.25</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,77 +1830,77 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.91</v>
+        <v>2.59</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="N11" t="n">
-        <v>3.75</v>
+        <v>2.99</v>
       </c>
       <c r="O11" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.8</v>
+        <v>3.93</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.27</v>
       </c>
       <c r="T11" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
         <v>1.36</v>
       </c>
-      <c r="X11" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>2.91</v>
+        <v>3.52</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.15</v>
+        <v>3.44</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T18" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X18" t="n">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="Y18" t="n">
         <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.12</v>
+        <v>4.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AC18" t="n">
         <v>1.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.09</v>
+        <v>3.85</v>
       </c>
       <c r="M2" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="O2" t="n">
         <v>3.7</v>
@@ -687,40 +687,40 @@
         <v>2.93</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="U2" t="n">
         <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA2" t="n">
         <v>4.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AC2" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD2" t="n">
         <v>1.8</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.26</v>
+        <v>2.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="T3" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,62 +927,62 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA4" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="AB4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.27</v>
       </c>
-      <c r="X4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.56</v>
+        <v>6.75</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>8.08</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>18.68</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.36</v>
       </c>
-      <c r="P5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>15</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.12</v>
-      </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>3.98</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.35</v>
+        <v>1.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.75</v>
+        <v>1.41</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.59</v>
+        <v>1.87</v>
       </c>
       <c r="M11" t="n">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.99</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.93</v>
+        <v>4.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.27</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="X11" t="n">
-        <v>2.51</v>
+        <v>2.69</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.79</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.62</v>
+        <v>4.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="M13" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
         <v>3.55</v>
@@ -2109,10 +2109,10 @@
         <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
         <v>1.36</v>
@@ -2127,16 +2127,16 @@
         <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
         <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AC13" t="n">
         <v>1.83</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y17" t="n">
         <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,62 +798,62 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O3" t="n">
-        <v>2.75</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="AB3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.27</v>
       </c>
-      <c r="X3" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.56</v>
+        <v>6.75</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="M4" t="n">
-        <v>10.5</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.36</v>
       </c>
-      <c r="P4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>15</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.12</v>
-      </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.08</v>
+        <v>3.98</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>1.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.75</v>
+        <v>1.41</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="T5" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="U5" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.56</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,43 +1572,43 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
         <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Y9" t="n">
         <v>2.5</v>
@@ -1617,16 +1617,16 @@
         <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.65</v>
+        <v>2.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="Q10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.26</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.35</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,77 +1830,77 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.35</v>
       </c>
-      <c r="N11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.26</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.36</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.8</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,62 +2346,62 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
       <c r="AE15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,62 +2475,62 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="R16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.4</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>3.94</v>
       </c>
       <c r="O17" t="n">
-        <v>3.52</v>
+        <v>2.91</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.44</v>
+        <v>4.15</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X17" t="n">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="Y17" t="n">
         <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.65</v>
+        <v>4.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
         <v>1.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,58 +3249,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="O22" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.08</v>
+        <v>3.92</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
         <v>3.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AD22" t="n">
         <v>1.74</v>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="N23" t="n">
         <v>3.3</v>
@@ -3399,25 +3399,25 @@
         <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="T23" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="U23" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="V23" t="n">
         <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X23" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="Z23" t="n">
         <v>1.36</v>
@@ -3426,13 +3426,13 @@
         <v>5.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
         <v>1.57</v>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="N26" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="O26" t="n">
         <v>2.35</v>
@@ -3783,7 +3783,7 @@
         <v>4.68</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
         <v>2.85</v>
@@ -3798,10 +3798,10 @@
         <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X26" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="Y26" t="n">
         <v>1.85</v>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
         <v>1.83</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -684,28 +684,28 @@
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
         <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="X2" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="Y2" t="n">
         <v>2.3</v>
@@ -714,13 +714,13 @@
         <v>1.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AD2" t="n">
         <v>1.8</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
         <v>3.26</v>
@@ -948,13 +948,13 @@
         <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="T4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
@@ -966,13 +966,13 @@
         <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z4" t="n">
         <v>1.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="AB4" t="n">
         <v>1.17</v>
@@ -981,7 +981,7 @@
         <v>1.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1056,28 +1056,28 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="P5" t="n">
         <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T5" t="n">
         <v>2.79</v>
@@ -1089,16 +1089,16 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
         <v>3.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AA5" t="n">
         <v>3.4</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
         <v>2.85</v>
@@ -1347,16 +1347,16 @@
         <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
         <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AA7" t="n">
         <v>5.83</v>
@@ -1572,43 +1572,43 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Y9" t="n">
         <v>2.5</v>
@@ -1617,16 +1617,16 @@
         <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>2.54</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
         <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.65</v>
+        <v>2.52</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.26</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.35</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="X11" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2619,13 +2619,13 @@
         <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
         <v>3.25</v>
@@ -2640,7 +2640,7 @@
         <v>1.44</v>
       </c>
       <c r="X17" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="Y17" t="n">
         <v>2.3</v>
@@ -2652,13 +2652,13 @@
         <v>4.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2742,31 +2742,31 @@
         <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S18" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="T18" t="n">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="U18" t="n">
         <v>1.22</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="X18" t="n">
         <v>2.49</v>
@@ -2784,10 +2784,10 @@
         <v>1.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="M23" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="N23" t="n">
         <v>3.3</v>
@@ -3411,13 +3411,13 @@
         <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X23" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="Z23" t="n">
         <v>1.36</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="M26" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>2.35</v>
@@ -3804,10 +3804,10 @@
         <v>3.28</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AA26" t="n">
         <v>3.04</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.04</v>
+        <v>2.15</v>
       </c>
       <c r="M3" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.36</v>
       </c>
-      <c r="P3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>15</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.66</v>
-      </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>3.14</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.43</v>
+        <v>1.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.35</v>
+        <v>1.73</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.95</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>6.75</v>
+        <v>1.56</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.55</v>
       </c>
-      <c r="M4" t="n">
+      <c r="AA4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC4" t="n">
         <v>3.35</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.81</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.41</v>
+        <v>6.75</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,77 +1056,77 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.1</v>
       </c>
-      <c r="O5" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.79</v>
-      </c>
       <c r="U5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.36</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X5" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.26</v>
       </c>
-      <c r="AC5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>2.52</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R10" t="n">
         <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T10" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.41</v>
+        <v>1.82</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
         <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,62 +2346,62 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="R15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.4</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>2.78</v>
+        <v>3.55</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD15" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.34</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.22</v>
       </c>
-      <c r="X16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,77 +798,77 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.1</v>
       </c>
-      <c r="O3" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.79</v>
-      </c>
       <c r="U3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.36</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X3" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AB3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.26</v>
       </c>
-      <c r="AC3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.04</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.36</v>
       </c>
-      <c r="P4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>15</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.66</v>
-      </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>3.14</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>1.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>1.73</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>1.95</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.75</v>
+        <v>1.56</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>15</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.55</v>
       </c>
-      <c r="M5" t="n">
+      <c r="AA5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC5" t="n">
         <v>3.35</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.81</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.41</v>
+        <v>6.75</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="M7" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
       <c r="N8" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -819,7 +819,7 @@
         <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="T3" t="n">
         <v>3.1</v>
@@ -868,7 +868,7 @@
         <v>1.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>1.04</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>25</v>
       </c>
       <c r="O4" t="n">
-        <v>2.77</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA4" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AB4" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.73</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.95</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.56</v>
+        <v>6.75</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.04</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.36</v>
       </c>
-      <c r="P5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>15</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.66</v>
-      </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>1.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.35</v>
+        <v>1.73</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>1.95</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.75</v>
+        <v>1.56</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1710,19 +1710,19 @@
         <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
         <v>3.26</v>
@@ -1734,10 +1734,10 @@
         <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X10" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
         <v>2.25</v>
@@ -1749,13 +1749,13 @@
         <v>4.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.34</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.22</v>
       </c>
-      <c r="X15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AC15" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,62 +2475,62 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="R16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.4</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>2.78</v>
+        <v>3.55</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2751,16 +2751,16 @@
         <v>3.48</v>
       </c>
       <c r="R18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S18" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="T18" t="n">
         <v>3.48</v>
       </c>
       <c r="U18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="V18" t="n">
         <v>1.05</v>
@@ -2769,7 +2769,7 @@
         <v>1.49</v>
       </c>
       <c r="X18" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="Y18" t="n">
         <v>2.3</v>
@@ -2778,16 +2778,16 @@
         <v>1.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AB18" t="n">
         <v>1.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>3.71</v>
+        <v>3.84</v>
       </c>
       <c r="O21" t="n">
         <v>2.65</v>
@@ -3147,22 +3147,22 @@
         <v>3.7</v>
       </c>
       <c r="U21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V21" t="n">
         <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AA21" t="n">
         <v>5.3</v>
@@ -3171,7 +3171,7 @@
         <v>1.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD21" t="n">
         <v>1.6</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3774,16 +3774,16 @@
         <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.68</v>
+        <v>4.57</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
         <v>2.85</v>
@@ -3798,7 +3798,7 @@
         <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X26" t="n">
         <v>3.28</v>
@@ -3810,16 +3810,16 @@
         <v>1.82</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="O2" t="n">
         <v>3.7</v>
@@ -684,7 +684,7 @@
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
@@ -693,10 +693,10 @@
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
         <v>1.08</v>
@@ -708,10 +708,10 @@
         <v>2.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AA2" t="n">
         <v>3.9</v>
@@ -720,7 +720,7 @@
         <v>1.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD2" t="n">
         <v>1.8</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
         <v>3.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
         <v>3.16</v>
@@ -837,7 +837,7 @@
         <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z3" t="n">
         <v>1.6</v>
@@ -868,7 +868,7 @@
         <v>1.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -930,10 +930,10 @@
         <v>1.04</v>
       </c>
       <c r="M4" t="n">
-        <v>10.5</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>20.64</v>
       </c>
       <c r="O4" t="n">
         <v>1.36</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="M5" t="n">
         <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>2.77</v>
@@ -1071,7 +1071,7 @@
         <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="R5" t="n">
         <v>1.37</v>
@@ -1080,10 +1080,10 @@
         <v>2.76</v>
       </c>
       <c r="T5" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1092,22 +1092,22 @@
         <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB5" t="n">
         <v>1.26</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD5" t="n">
         <v>1.95</v>
@@ -1191,55 +1191,55 @@
         <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="Z6" t="n">
         <v>1.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
       <c r="N7" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>2.49</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
         <v>1.03</v>
       </c>
       <c r="W10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.37</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.81</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.5</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X11" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.3</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA12" t="n">
         <v>3.7</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="M14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T14" t="n">
         <v>3.2</v>
       </c>
-      <c r="N14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="U14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2346,19 +2346,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.23</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
         <v>3.45</v>
@@ -2370,7 +2370,7 @@
         <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
         <v>1.3</v>
@@ -2382,26 +2382,26 @@
         <v>1.34</v>
       </c>
       <c r="X15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AA15" t="n">
         <v>4</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.84</v>
       </c>
-      <c r="AD15" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2484,34 +2484,34 @@
         <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="R16" t="n">
         <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
         <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Y16" t="n">
         <v>1.93</v>
@@ -2520,16 +2520,16 @@
         <v>1.77</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="O18" t="n">
         <v>3.25</v>
@@ -2748,46 +2748,46 @@
         <v>1.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S18" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="T18" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="U18" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="W18" t="n">
         <v>1.49</v>
       </c>
       <c r="X18" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AB18" t="n">
         <v>1.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,31 +3249,31 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3.03</v>
+        <v>2.82</v>
       </c>
       <c r="O22" t="n">
-        <v>2.94</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.92</v>
+        <v>3.66</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="T22" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U22" t="n">
         <v>1.27</v>
@@ -3282,44 +3282,44 @@
         <v>1.03</v>
       </c>
       <c r="W22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.3</v>
       </c>
-      <c r="X22" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3390,7 +3390,7 @@
         <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="Q23" t="n">
         <v>4</v>
@@ -3399,13 +3399,13 @@
         <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="T23" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="V23" t="n">
         <v>1.14</v>
@@ -3426,7 +3426,7 @@
         <v>5.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AC23" t="n">
         <v>2.25</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,77 +798,77 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="M3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N3" t="n">
         <v>3</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O3" t="n">
-        <v>3.26</v>
+        <v>2.77</v>
       </c>
       <c r="P3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="Z3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.3</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -945,10 +945,10 @@
         <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T4" t="n">
         <v>2.07</v>
@@ -957,7 +957,7 @@
         <v>1.66</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,77 +1056,77 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.77</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>3.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="T5" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X5" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.26</v>
       </c>
-      <c r="AC5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>4.85</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,16 +1314,16 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="M7" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="P7" t="n">
         <v>1.79</v>
@@ -1335,7 +1335,7 @@
         <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
         <v>3.74</v>
@@ -1347,28 +1347,28 @@
         <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X7" t="n">
         <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AA7" t="n">
         <v>5.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>5.6</v>
+        <v>4.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,77 +1572,77 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.86</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
         <v>1.03</v>
       </c>
       <c r="W9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.37</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.81</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>1.86</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
         <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X10" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.1</v>
+        <v>4.51</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
         <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q14" t="n">
         <v>4.1</v>
       </c>
-      <c r="O14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.51</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
         <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="X14" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2475,77 +2475,77 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.95</v>
+        <v>4.47</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.89</v>
+        <v>2.61</v>
       </c>
       <c r="T16" t="n">
-        <v>2.61</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="X16" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.66</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.68</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.71</v>
+        <v>3.84</v>
       </c>
       <c r="O20" t="n">
         <v>2.65</v>
@@ -3018,25 +3018,25 @@
         <v>3.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
         <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="X20" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AB20" t="n">
         <v>1.15</v>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3378,19 +3378,19 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
         <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q23" t="n">
         <v>4</v>
@@ -3399,34 +3399,34 @@
         <v>1.57</v>
       </c>
       <c r="S23" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="T23" t="n">
         <v>4.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
         <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="X23" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Z23" t="n">
         <v>1.36</v>
       </c>
       <c r="AA23" t="n">
-        <v>5.6</v>
+        <v>5.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AC23" t="n">
         <v>2.25</v>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="N24" t="n">
-        <v>3.08</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="O26" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.57</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
@@ -3804,22 +3804,22 @@
         <v>3.28</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.88</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.82</v>
       </c>
       <c r="AA26" t="n">
         <v>3.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="O2" t="n">
         <v>3.7</v>
@@ -684,43 +684,43 @@
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
         <v>1.41</v>
       </c>
       <c r="X2" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AB2" t="n">
         <v>1.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD2" t="n">
         <v>1.8</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>2.77</v>
+        <v>3.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.8</v>
+        <v>3.16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="T3" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,77 +927,77 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.04</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>8.859999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>20.64</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>2.77</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>3.8</v>
       </c>
       <c r="R4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
         <v>1.33</v>
       </c>
-      <c r="S4" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AH4" t="n">
-        <v>6.75</v>
+        <v>1.56</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>20.64</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.16</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.43</v>
       </c>
-      <c r="S5" t="n">
+      <c r="Z5" t="n">
         <v>2.55</v>
       </c>
-      <c r="T5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AA5" t="n">
-        <v>3.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.88</v>
+        <v>3.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.81</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.41</v>
+        <v>6.75</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="M7" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1443,19 +1443,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="N8" t="n">
-        <v>4.85</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
         <v>5.25</v>
@@ -1473,13 +1473,13 @@
         <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
         <v>1.43</v>
       </c>
       <c r="X8" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Y8" t="n">
         <v>2.3</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="P10" t="n">
         <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.5</v>
+        <v>5.12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
         <v>2.52</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
         <v>1.03</v>
@@ -1737,13 +1737,13 @@
         <v>1.37</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
         <v>4.6</v>
@@ -1755,7 +1755,7 @@
         <v>2.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
         <v>1.81</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>2.82</v>
+        <v>2.47</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.51</v>
+        <v>3.85</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
-        <v>2.65</v>
+        <v>3.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="P13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q13" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
         <v>1.72</v>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="O14" t="n">
         <v>2.87</v>
@@ -2346,19 +2346,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>3.23</v>
       </c>
       <c r="N15" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
         <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="Q15" t="n">
         <v>3.45</v>
@@ -2385,22 +2385,22 @@
         <v>2.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AA15" t="n">
         <v>4</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.84</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.4</v>
       </c>
-      <c r="O16" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.04</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="X16" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,43 +2604,43 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>3.94</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y17" t="n">
         <v>2.3</v>
@@ -2649,16 +2649,16 @@
         <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2733,16 +2733,16 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="P18" t="n">
         <v>1.82</v>
@@ -2754,7 +2754,7 @@
         <v>1.56</v>
       </c>
       <c r="S18" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="T18" t="n">
         <v>3.56</v>
@@ -2766,25 +2766,25 @@
         <v>1.11</v>
       </c>
       <c r="W18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X18" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AD18" t="n">
         <v>1.69</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2994,13 +2994,13 @@
         <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="N20" t="n">
-        <v>3.84</v>
+        <v>4.07</v>
       </c>
       <c r="O20" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="P20" t="n">
         <v>1.9</v>
@@ -3012,37 +3012,37 @@
         <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.44</v>
       </c>
-      <c r="X20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AA20" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
         <v>1.6</v>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3249,31 +3249,31 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="M22" t="n">
         <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="P22" t="n">
         <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U22" t="n">
         <v>1.27</v>
@@ -3285,22 +3285,22 @@
         <v>1.36</v>
       </c>
       <c r="X22" t="n">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="Y22" t="n">
         <v>2.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AD22" t="n">
         <v>1.73</v>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3378,77 +3378,77 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M23" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="N23" t="n">
         <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
         <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="S23" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="T23" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="U23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W23" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="X23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Y23" t="n">
         <v>3.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA23" t="n">
-        <v>5.85</v>
+        <v>5.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.54</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3765,25 +3765,25 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="M26" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
         <v>2.85</v>
@@ -3807,19 +3807,19 @@
         <v>1.85</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
         <v>3.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.55</v>
+        <v>1.15</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
-        <v>3.26</v>
+        <v>1.61</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.16</v>
+        <v>8.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="X3" t="n">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.95</v>
+        <v>2.56</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.41</v>
+        <v>3.64</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.04</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>8.859999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>20.64</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.36</v>
       </c>
-      <c r="P5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>15</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.12</v>
-      </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>3.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.35</v>
+        <v>1.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>1.81</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.75</v>
+        <v>1.41</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>2.7</v>
@@ -1218,16 +1218,16 @@
         <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
         <v>2.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AA6" t="n">
         <v>5.83</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="N7" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,31 +1701,31 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>2.44</v>
+        <v>3.62</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.12</v>
+        <v>3.26</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="T10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
         <v>1.27</v>
@@ -1734,28 +1734,28 @@
         <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.62</v>
+        <v>2.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.26</v>
+        <v>5.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="U11" t="n">
         <v>1.27</v>
@@ -1863,28 +1863,28 @@
         <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X11" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="N12" t="n">
         <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>2.47</v>
+        <v>2.82</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.85</v>
+        <v>4.51</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
-        <v>3.07</v>
+        <v>2.65</v>
       </c>
       <c r="Y12" t="n">
         <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="M13" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
         <v>3.55</v>
       </c>
       <c r="O13" t="n">
-        <v>2.82</v>
+        <v>2.47</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.51</v>
+        <v>3.85</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="X13" t="n">
-        <v>2.65</v>
+        <v>3.07</v>
       </c>
       <c r="Y13" t="n">
         <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.05</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.3</v>
       </c>
       <c r="O16" t="n">
         <v>2.86</v>
@@ -2514,10 +2514,10 @@
         <v>2.64</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
         <v>4.2</v>
@@ -2604,43 +2604,43 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>3.94</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>2.3</v>
@@ -2649,16 +2649,16 @@
         <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.01</v>
+        <v>2.86</v>
       </c>
       <c r="N20" t="n">
-        <v>4.07</v>
+        <v>3.71</v>
       </c>
       <c r="O20" t="n">
         <v>2.6</v>
@@ -3024,16 +3024,16 @@
         <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AA20" t="n">
         <v>5.2</v>
@@ -3249,19 +3249,19 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="M22" t="n">
         <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
         <v>3.3</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q22" t="n">
         <v>3.5</v>
@@ -3270,40 +3270,40 @@
         <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T22" t="n">
         <v>3.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
         <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="X22" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="M23" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
         <v>3.2</v>
@@ -3411,13 +3411,13 @@
         <v>1.15</v>
       </c>
       <c r="W23" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="X23" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="Z23" t="n">
         <v>1.33</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>2.55</v>
@@ -3804,10 +3804,10 @@
         <v>3.28</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AA26" t="n">
         <v>3.05</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -681,31 +681,31 @@
         <v>3.7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="Y2" t="n">
         <v>2.3</v>
@@ -714,13 +714,13 @@
         <v>1.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="AB2" t="n">
         <v>1.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AD2" t="n">
         <v>1.8</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.15</v>
+        <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>6.4</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.61</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.1</v>
+        <v>3.16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>3.85</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.64</v>
+        <v>1.48</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -936,13 +936,13 @@
         <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
@@ -951,7 +951,7 @@
         <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="U4" t="n">
         <v>1.38</v>
@@ -975,7 +975,7 @@
         <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" t="n">
         <v>1.7</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.55</v>
+        <v>1.14</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>17</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>1.72</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.16</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
         <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="X5" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.95</v>
+        <v>2.46</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.88</v>
+        <v>2.51</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.41</v>
+        <v>3.7</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="M7" t="n">
-        <v>3.56</v>
+        <v>2.86</v>
       </c>
       <c r="N7" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.25</v>
+        <v>5.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.43</v>
+        <v>2.24</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="N8" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1581,28 +1581,28 @@
         <v>2.93</v>
       </c>
       <c r="O9" t="n">
-        <v>3.09</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="T9" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
         <v>1.5</v>
@@ -1617,16 +1617,16 @@
         <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.81</v>
+        <v>5.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1710,31 +1710,31 @@
         <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>3.62</v>
+        <v>3.43</v>
       </c>
       <c r="P10" t="n">
         <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="R10" t="n">
         <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
         <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X10" t="n">
         <v>2.62</v>
@@ -1749,13 +1749,13 @@
         <v>4.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1839,25 +1839,25 @@
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.12</v>
+        <v>4.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="T11" t="n">
         <v>3.35</v>
       </c>
       <c r="U11" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
         <v>1.03</v>
@@ -1875,16 +1875,16 @@
         <v>1.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="M12" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>3.31</v>
       </c>
       <c r="O12" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.51</v>
+        <v>4.21</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V12" t="n">
         <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="X12" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.3</v>
+        <v>3.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2097,34 +2097,34 @@
         <v>3.55</v>
       </c>
       <c r="O13" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.85</v>
+        <v>4.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="T13" t="n">
         <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
         <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>3.07</v>
+        <v>3.02</v>
       </c>
       <c r="Y13" t="n">
         <v>2.25</v>
@@ -2133,16 +2133,16 @@
         <v>1.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
         <v>1.67</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="M14" t="n">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="N14" t="n">
-        <v>3.31</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.1</v>
+        <v>4.47</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
         <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X14" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="P15" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.3</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.25</v>
+        <v>3.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="X16" t="n">
-        <v>2.64</v>
+        <v>2.81</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AB16" t="n">
         <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2742,16 +2742,16 @@
         <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>3.26</v>
+        <v>3.47</v>
       </c>
       <c r="P18" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.18</v>
+        <v>3.45</v>
       </c>
       <c r="R18" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S18" t="n">
         <v>2.29</v>
@@ -2760,10 +2760,10 @@
         <v>3.56</v>
       </c>
       <c r="U18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="V18" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
         <v>1.48</v>
@@ -2781,10 +2781,10 @@
         <v>5.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
         <v>1.69</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.51</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="O22" t="n">
         <v>3.3</v>
@@ -3291,7 +3291,7 @@
         <v>2.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AA22" t="n">
         <v>4.4</v>
@@ -3387,28 +3387,28 @@
         <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="P23" t="n">
         <v>1.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="S23" t="n">
         <v>2.1</v>
       </c>
       <c r="T23" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V23" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="W23" t="n">
         <v>1.62</v>
@@ -3423,16 +3423,16 @@
         <v>1.33</v>
       </c>
       <c r="AA23" t="n">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3774,13 +3774,13 @@
         <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.7</v>
+        <v>4.13</v>
       </c>
       <c r="R26" t="n">
         <v>1.35</v>
@@ -3798,7 +3798,7 @@
         <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
         <v>3.28</v>
@@ -3816,10 +3816,10 @@
         <v>1.28</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -1572,43 +1572,43 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Y9" t="n">
         <v>2.5</v>
@@ -1617,16 +1617,16 @@
         <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.55</v>
+        <v>1.14</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>17</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>1.72</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.16</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
         <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.2</v>
+        <v>2.46</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.9</v>
+        <v>2.51</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.48</v>
+        <v>1.05</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.48</v>
+        <v>3.7</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.14</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>17</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>1.72</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>3.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
         <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="X5" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.51</v>
+        <v>1.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.7</v>
+        <v>1.48</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.43</v>
+        <v>2.55</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="R10" t="n">
         <v>1.48</v>
@@ -1725,7 +1725,7 @@
         <v>2.45</v>
       </c>
       <c r="T10" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="U10" t="n">
         <v>1.3</v>
@@ -1734,28 +1734,28 @@
         <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="X10" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.55</v>
+        <v>3.43</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="R11" t="n">
         <v>1.48</v>
@@ -1854,7 +1854,7 @@
         <v>2.45</v>
       </c>
       <c r="T11" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="U11" t="n">
         <v>1.3</v>
@@ -1863,44 +1863,44 @@
         <v>1.03</v>
       </c>
       <c r="W11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
         <v>1.37</v>
       </c>
-      <c r="X11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
         <v>3.55</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.43</v>
+        <v>4.47</v>
       </c>
       <c r="R13" t="n">
         <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.69</v>
+        <v>2.52</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X13" t="n">
-        <v>3.02</v>
+        <v>2.66</v>
       </c>
       <c r="Y13" t="n">
         <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="M14" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
         <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.47</v>
+        <v>4.43</v>
       </c>
       <c r="R14" t="n">
         <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.52</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>2.66</v>
+        <v>3.02</v>
       </c>
       <c r="Y14" t="n">
         <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
         <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45901.66666666666</v>
+        <v>45901.64583333334</v>
       </c>
     </row>
     <row r="16">
@@ -2475,19 +2475,19 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
         <v>3.45</v>
@@ -2499,37 +2499,37 @@
         <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X16" t="n">
         <v>2.81</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.85</v>
+        <v>3.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
         <v>1.93</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45901.6875</v>
+        <v>45901.66666666666</v>
       </c>
     </row>
     <row r="18">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45901.75</v>
+        <v>45901.6875</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45901.79166666666</v>
+        <v>45901.75</v>
       </c>
     </row>
     <row r="21">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,25 +3249,25 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="N22" t="n">
-        <v>3.03</v>
+        <v>3.71</v>
       </c>
       <c r="O22" t="n">
-        <v>3.3</v>
+        <v>2.51</v>
       </c>
       <c r="P22" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>5.13</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S22" t="n">
         <v>2.4</v>
@@ -3276,34 +3276,34 @@
         <v>3.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y22" t="n">
         <v>2.62</v>
       </c>
-      <c r="Y22" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Z22" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45901.83333333334</v>
+        <v>45901.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,77 +3378,77 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>2.7</v>
+        <v>3.17</v>
       </c>
       <c r="N23" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O23" t="n">
         <v>3.3</v>
       </c>
-      <c r="O23" t="n">
-        <v>3.12</v>
-      </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="T23" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.18</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Z23" t="n">
+      <c r="AC23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>1.33</v>
       </c>
-      <c r="AA23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45901.88541666666</v>
+        <v>45901.83333333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="X24" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45901.89583333334</v>
+        <v>45901.88541666666</v>
       </c>
     </row>
     <row r="25">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3724,126 +3724,255 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Montego Bay United</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Treasure Beach</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3" t="n">
+        <v>45901.89583333334</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Bay</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>1.97</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>3.45</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N27" t="n">
         <v>3.5</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O27" t="n">
         <v>2.53</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P27" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q27" t="n">
         <v>4.13</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>1.35</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S27" t="n">
         <v>2.85</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>2.68</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>1.39</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V27" t="n">
         <v>1.02</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W27" t="n">
         <v>1.25</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X27" t="n">
         <v>3.28</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Y27" t="n">
         <v>1.88</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="Z27" t="n">
         <v>1.82</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AA27" t="n">
         <v>3.05</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AB27" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AC27" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AD27" t="n">
         <v>1.95</v>
       </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.23</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AH27" t="n">
         <v>1.69</v>
       </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="3" t="n">
         <v>45901.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,77 +798,77 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.14</v>
+        <v>2.15</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>17</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.72</v>
+        <v>2.74</v>
       </c>
       <c r="P3" t="n">
-        <v>2.62</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.25</v>
       </c>
-      <c r="S3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="AH3" t="n">
         <v>1.62</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>3.7</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>1.14</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="O4" t="n">
-        <v>2.74</v>
+        <v>1.72</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.62</v>
       </c>
       <c r="Q4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S4" t="n">
         <v>3.6</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T4" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="X4" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.7</v>
+        <v>2.51</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.62</v>
+        <v>3.7</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="N8" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.05</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.75</v>
-      </c>
       <c r="O16" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="T16" t="n">
         <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W16" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X16" t="n">
-        <v>2.81</v>
+        <v>2.49</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AB16" t="n">
         <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O17" t="n">
         <v>3.15</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.84</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
         <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
-        <v>2.49</v>
+        <v>2.81</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AB17" t="n">
         <v>1.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3249,28 +3249,28 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.71</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.13</v>
+        <v>4.65</v>
       </c>
       <c r="R22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T22" t="n">
         <v>3.3</v>
@@ -3282,28 +3282,28 @@
         <v>1.11</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X22" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="Y22" t="n">
         <v>2.62</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AB22" t="n">
         <v>1.16</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.29</v>
+        <v>2.51</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -669,28 +669,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="N2" t="n">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
         <v>2.88</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
         <v>3.15</v>
@@ -699,31 +699,31 @@
         <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X2" t="n">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="Y2" t="n">
         <v>2.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.88</v>
+        <v>3.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" t="n">
         <v>1.97</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.1</v>
       </c>
-      <c r="O3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.8</v>
-      </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -936,34 +936,34 @@
         <v>17</v>
       </c>
       <c r="O4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="P4" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y4" t="n">
         <v>1.55</v>
@@ -972,16 +972,16 @@
         <v>2.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.51</v>
+        <v>1.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,77 +1056,77 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="R5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.43</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.48</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="M7" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="M8" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="P8" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.25</v>
+        <v>7.13</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="Y8" t="n">
         <v>2.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1590,13 +1590,13 @@
         <v>3.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
         <v>2.23</v>
       </c>
       <c r="T9" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="U9" t="n">
         <v>1.18</v>
@@ -1617,10 +1617,10 @@
         <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AC9" t="n">
         <v>2.26</v>
@@ -1642,7 +1642,7 @@
         <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>2.55</v>
+        <v>3.44</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
         <v>1.48</v>
@@ -1725,7 +1725,7 @@
         <v>2.45</v>
       </c>
       <c r="T10" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
         <v>1.3</v>
@@ -1734,28 +1734,28 @@
         <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="X10" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.43</v>
+        <v>2.55</v>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="U11" t="n">
         <v>1.3</v>
@@ -1863,28 +1863,28 @@
         <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="X11" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="P12" t="n">
         <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.21</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
@@ -1983,37 +1983,37 @@
         <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="U12" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
         <v>1.33</v>
       </c>
       <c r="X12" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="M13" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.47</v>
+        <v>4.16</v>
       </c>
       <c r="R13" t="n">
         <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="X13" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.43</v>
+        <v>4.54</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
         <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Z14" t="n">
         <v>1.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
         <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="M16" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O16" t="n">
         <v>3.15</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.84</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
         <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="X16" t="n">
-        <v>2.49</v>
+        <v>2.81</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AB16" t="n">
         <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N17" t="n">
         <v>3.05</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.75</v>
-      </c>
       <c r="O17" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X17" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2751,13 +2751,13 @@
         <v>3.45</v>
       </c>
       <c r="R18" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="S18" t="n">
         <v>2.29</v>
       </c>
       <c r="T18" t="n">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="U18" t="n">
         <v>1.25</v>
@@ -2787,7 +2787,7 @@
         <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AH18" t="n">
         <v>1.39</v>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.82</v>
+        <v>1.15</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="O22" t="n">
-        <v>2.49</v>
+        <v>1.43</v>
       </c>
       <c r="P22" t="n">
-        <v>2.02</v>
+        <v>3.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.65</v>
+        <v>11.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="S22" t="n">
-        <v>2.36</v>
+        <v>4.4</v>
       </c>
       <c r="T22" t="n">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
       <c r="U22" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>2.63</v>
+        <v>6.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.62</v>
+        <v>1.32</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.41</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>5</v>
+        <v>1.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.16</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.99</v>
+        <v>5.2</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3393,13 +3393,13 @@
         <v>1.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
         <v>1.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
         <v>3.3</v>
@@ -3408,7 +3408,7 @@
         <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
         <v>1.45</v>
@@ -3423,10 +3423,10 @@
         <v>1.53</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC23" t="n">
         <v>1.93</v>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="P24" t="n">
         <v>1.8</v>
@@ -3534,7 +3534,7 @@
         <v>3.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V24" t="n">
         <v>1.1</v>
@@ -3558,7 +3558,7 @@
         <v>1.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD24" t="n">
         <v>1.51</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5.77</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3903,13 +3903,13 @@
         <v>3.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.13</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
         <v>1.35</v>
@@ -3921,7 +3921,7 @@
         <v>2.68</v>
       </c>
       <c r="U27" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
         <v>1.02</v>
@@ -3964,7 +3964,7 @@
         <v>1.23</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -652,20 +652,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -727,12 +727,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
         <v>2.83</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="U3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.3</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.36</v>
-      </c>
       <c r="X3" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AA3" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AB3" t="n">
         <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,58 +927,58 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>4.55</v>
       </c>
       <c r="N4" t="n">
-        <v>17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="P4" t="n">
-        <v>2.46</v>
+        <v>2.19</v>
       </c>
       <c r="Q4" t="n">
         <v>8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>2.76</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="U4" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X4" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
         <v>1.49</v>
@@ -997,7 +997,7 @@
         <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>3.46</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="O5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA5" t="n">
         <v>3.08</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.28</v>
-      </c>
       <c r="AB5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1572,19 +1572,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="M9" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="N9" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="O9" t="n">
         <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
         <v>3.75</v>
@@ -1593,40 +1593,40 @@
         <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="T9" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.07</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.44</v>
+        <v>2.84</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
         <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="T10" t="n">
         <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V10" t="n">
         <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="AB10" t="n">
         <v>1.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
         <v>2.55</v>
@@ -1845,22 +1845,22 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="R11" t="n">
         <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
         <v>3.35</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
         <v>1.39</v>
@@ -1869,22 +1869,22 @@
         <v>2.59</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AA11" t="n">
         <v>4.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2733,31 +2733,31 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="N18" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="O18" t="n">
-        <v>3.47</v>
+        <v>3.34</v>
       </c>
       <c r="P18" t="n">
         <v>1.89</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="R18" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="T18" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="U18" t="n">
         <v>1.25</v>
@@ -2772,10 +2772,10 @@
         <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA18" t="n">
         <v>5.3</v>
@@ -2787,7 +2787,7 @@
         <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -781,20 +781,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '45+1']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '36', '62', '90+2']</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -910,20 +910,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -985,7 +985,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39', '65']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1039,20 +1039,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '89']</t>
         </is>
       </c>
       <c r="AG5" t="n">
@@ -1149,113 +1149,113 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.91</v>
+        <v>1.51</v>
       </c>
       <c r="M6" t="n">
-        <v>2.86</v>
+        <v>3.45</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.86</v>
+        <v>2.11</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.03</v>
+        <v>7.13</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>2.16</v>
+        <v>2.49</v>
       </c>
       <c r="T6" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="X6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y6" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y6" t="n">
-        <v>2.77</v>
-      </c>
       <c r="Z6" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '26', '29']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.65</v>
+        <v>2.24</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,113 +1407,113 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>2.81</v>
       </c>
       <c r="N8" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.11</v>
+        <v>3.12</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.13</v>
+        <v>4.26</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="X8" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '77', '86']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.24</v>
+        <v>1.57</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="M9" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="P9" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.75</v>
+        <v>4.55</v>
       </c>
       <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z9" t="n">
         <v>1.57</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AA9" t="n">
-        <v>5.95</v>
+        <v>4.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,16 +1804,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1826,81 +1826,81 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.09</v>
+        <v>2.37</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="T11" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X11" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="AB11" t="n">
         <v>1.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>['90+7']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="P12" t="n">
         <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>4.16</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X12" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.42</v>
+        <v>4.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="P13" t="n">
         <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.16</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
         <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="T13" t="n">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X13" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.05</v>
+        <v>3.42</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="M15" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.26</v>
       </c>
       <c r="O16" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X16" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2.82</v>
+        <v>3.12</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
-        <v>2.87</v>
+        <v>3.13</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="AB17" t="n">
         <v>1.18</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>2.51</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>2.79</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="O20" t="n">
         <v>2.89</v>
@@ -3030,10 +3030,10 @@
         <v>4</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="AA20" t="n">
         <v>2.55</v>
@@ -3120,49 +3120,49 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="M21" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3.71</v>
+        <v>4.51</v>
       </c>
       <c r="O21" t="n">
         <v>2.49</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="Q21" t="n">
         <v>4.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S21" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="U21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V21" t="n">
         <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AA21" t="n">
         <v>5</v>
@@ -3171,10 +3171,10 @@
         <v>1.16</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="O22" t="n">
         <v>1.43</v>
@@ -3288,16 +3288,16 @@
         <v>6.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.32</v>
+        <v>1.95</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>1.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
         <v>2</v>
@@ -3378,28 +3378,28 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.03</v>
+        <v>3.7</v>
       </c>
       <c r="O23" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="P23" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>4.47</v>
       </c>
       <c r="R23" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="T23" t="n">
         <v>3.3</v>
@@ -3411,28 +3411,28 @@
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X23" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>3.24</v>
@@ -3528,10 +3528,10 @@
         <v>1.58</v>
       </c>
       <c r="S24" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T24" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U24" t="n">
         <v>1.17</v>
@@ -3540,16 +3540,16 @@
         <v>1.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="X24" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Y24" t="n">
         <v>3.04</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AA24" t="n">
         <v>7</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.29</v>
+        <v>1.51</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.08</v>
+        <v>5.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,49 +3765,49 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.5</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3894,22 +3894,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
         <v>3.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
         <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="R27" t="n">
         <v>1.35</v>
@@ -3921,7 +3921,7 @@
         <v>2.68</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V27" t="n">
         <v>1.02</v>
@@ -3933,10 +3933,10 @@
         <v>3.28</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AA27" t="n">
         <v>3.05</v>
@@ -3945,10 +3945,10 @@
         <v>1.28</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,77 +798,77 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.52</v>
+        <v>3.46</v>
       </c>
       <c r="M3" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="N3" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="O3" t="n">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="T3" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="U3" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['32', '45+1']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['22', '36', '62', '90+2']</t>
+          <t>['19', '89']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,77 +927,77 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>2.52</v>
       </c>
       <c r="M4" t="n">
-        <v>4.55</v>
+        <v>3.26</v>
       </c>
       <c r="N4" t="n">
-        <v>9.199999999999999</v>
+        <v>2.16</v>
       </c>
       <c r="O4" t="n">
-        <v>1.82</v>
+        <v>3.34</v>
       </c>
       <c r="P4" t="n">
-        <v>2.19</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>2.83</v>
       </c>
       <c r="R4" t="n">
         <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T4" t="n">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X4" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>1.79</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.49</v>
+        <v>1.87</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['39', '65']</t>
+          <t>['32', '45+1']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '36', '62', '90+2']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.2</v>
+        <v>1.32</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,46 +1056,46 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.46</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
-        <v>3.24</v>
+        <v>4.55</v>
       </c>
       <c r="N5" t="n">
-        <v>2.11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>3.64</v>
+        <v>1.82</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="T5" t="n">
-        <v>2.86</v>
+        <v>2.55</v>
       </c>
       <c r="U5" t="n">
         <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
         <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Z5" t="n">
         <v>1.83</v>
@@ -1104,29 +1104,29 @@
         <v>3.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.69</v>
+        <v>2.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.03</v>
+        <v>1.49</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['39', '65']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['19', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.31</v>
+        <v>3.2</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1174,10 +1174,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,77 +1185,77 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="M6" t="n">
-        <v>3.45</v>
+        <v>2.81</v>
       </c>
       <c r="N6" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.11</v>
+        <v>3.12</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.13</v>
+        <v>4.26</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="X6" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['8', '26', '29']</t>
+          <t>['4', '77', '86']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.24</v>
+        <v>1.57</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,103 +1288,103 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z7" t="n">
         <v>1.56</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '26', '29']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,113 +1407,113 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.4</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>2.81</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['4', '77', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,16 +1675,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1697,81 +1697,81 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
+          <t>['90+7']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,16 +1804,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1826,69 +1826,69 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['90+7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,91 +1933,91 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="P12" t="n">
         <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.16</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X12" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.05</v>
+        <v>3.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '36', '61']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2029,7 +2029,7 @@
         <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,19 +2062,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2084,81 +2084,81 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="P13" t="n">
         <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>4.16</v>
       </c>
       <c r="R13" t="n">
         <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X13" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.42</v>
+        <v>4.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '53']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60', '62', '79']</t>
         </is>
       </c>
       <c r="AG13" t="n">
         <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2200,20 +2200,20 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '87']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AG14" t="n">
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2439,97 +2439,97 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.1</v>
       </c>
-      <c r="N16" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X16" t="n">
-        <v>2.78</v>
+        <v>3.13</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2538,14 +2538,14 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '51']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,113 +2568,113 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>3.26</v>
       </c>
       <c r="O17" t="n">
-        <v>3.12</v>
+        <v>2.84</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X17" t="n">
-        <v>3.13</v>
+        <v>2.78</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
+          <t>['11', '26', '57', '80']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2716,94 +2716,94 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '33']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['72', '87']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2845,20 +2845,20 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31', '84']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AG19" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.82</v>
+        <v>1.19</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="N21" t="n">
-        <v>4.51</v>
+        <v>11.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.49</v>
+        <v>1.43</v>
       </c>
       <c r="P21" t="n">
-        <v>2.01</v>
+        <v>3.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.65</v>
+        <v>11.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>2.37</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
-        <v>3.55</v>
+        <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>2.45</v>
+        <v>6.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.16</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="M22" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>11.5</v>
+        <v>4.27</v>
       </c>
       <c r="O22" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="P22" t="n">
-        <v>3.14</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>11.4</v>
+        <v>5.28</v>
       </c>
       <c r="R22" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>4.4</v>
+        <v>2.36</v>
       </c>
       <c r="T22" t="n">
-        <v>1.93</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.79</v>
+        <v>1.23</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="X22" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>4.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>1.16</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>5.2</v>
+        <v>1.86</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3381,34 +3381,34 @@
         <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.47</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
         <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="T23" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
         <v>1.42</v>
@@ -3417,22 +3417,22 @@
         <v>2.75</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.05</v>
+        <v>3.92</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.51</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.57</v>
+        <v>1.51</v>
       </c>
       <c r="M26" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3894,31 +3894,31 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="N27" t="n">
         <v>3.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="T27" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="U27" t="n">
         <v>1.39</v>
@@ -3936,16 +3936,16 @@
         <v>1.91</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AB27" t="n">
         <v>1.28</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AD27" t="n">
         <v>1.91</v>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>

--- a/jogos_2025-09-01.xlsx
+++ b/jogos_2025-09-01.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,46 +798,46 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.46</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
-        <v>3.24</v>
+        <v>4.55</v>
       </c>
       <c r="N3" t="n">
-        <v>2.11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>3.64</v>
+        <v>1.82</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="T3" t="n">
-        <v>2.86</v>
+        <v>2.55</v>
       </c>
       <c r="U3" t="n">
         <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
         <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Z3" t="n">
         <v>1.83</v>
@@ -846,29 +846,29 @@
         <v>3.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.69</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.03</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['39', '65']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['19', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.31</v>
+        <v>3.2</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,72 +1030,72 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.29</v>
+        <v>3.46</v>
       </c>
       <c r="M5" t="n">
-        <v>4.55</v>
+        <v>3.24</v>
       </c>
       <c r="N5" t="n">
-        <v>9.199999999999999</v>
+        <v>2.11</v>
       </c>
       <c r="O5" t="n">
-        <v>1.82</v>
+        <v>3.64</v>
       </c>
       <c r="P5" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="T5" t="n">
-        <v>2.55</v>
+        <v>2.86</v>
       </c>
       <c r="U5" t="n">
         <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
         <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="Z5" t="n">
         <v>1.83</v>
@@ -1104,29 +1104,29 @@
         <v>3.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.35</v>
+        <v>1.69</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.49</v>
+        <v>2.03</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['39', '65']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '89']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.2</v>
+        <v>1.31</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1826,65 +1826,65 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.55</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="X11" t="n">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2439,35 +2439,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,77 +2475,77 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.26</v>
       </c>
       <c r="O16" t="n">
-        <v>3.12</v>
+        <v>2.84</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X16" t="n">
-        <v>3.13</v>
+        <v>2.78</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
+          <t>['11', '26', '57', '80']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['3', '51']</t>
-        </is>
-      </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,113 +2568,113 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="Q17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T17" t="n">
         <v>3.1</v>
       </c>
-      <c r="N17" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
-        <v>2.78</v>
+        <v>3.13</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['11', '26', '57', '80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '51']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2716,94 +2716,94 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['1', '33']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['72', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2974,94 +2974,94 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>2.25</v>
       </c>
       <c r="M20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3.2</v>
       </c>
-      <c r="N20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.18</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="V20" t="n">
         <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '69']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '40', '42']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,113 +3084,113 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>11.5</v>
+        <v>4.27</v>
       </c>
       <c r="O21" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="P21" t="n">
-        <v>3.14</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>11.4</v>
+        <v>5.28</v>
       </c>
       <c r="R21" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>4.4</v>
+        <v>2.36</v>
       </c>
       <c r="T21" t="n">
-        <v>1.93</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.79</v>
+        <v>1.23</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>4.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.16</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '62']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+10', '64']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>5.2</v>
+        <v>1.86</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,29 +3213,29 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3245,81 +3245,81 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>1.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>7.7</v>
       </c>
       <c r="N22" t="n">
-        <v>4.27</v>
+        <v>15</v>
       </c>
       <c r="O22" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="P22" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>11</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T22" t="n">
         <v>1.97</v>
       </c>
-      <c r="Q22" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.23</v>
+        <v>1.75</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.6</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.42</v>
+        <v>2.83</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.75</v>
+        <v>1.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.16</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.86</v>
+        <v>5.15</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="M24" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
         <v>3.24</v>
@@ -3522,46 +3522,46 @@
         <v>1.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S24" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="T24" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="U24" t="n">
         <v>1.17</v>
       </c>
       <c r="V24" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W24" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="X24" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Y24" t="n">
         <v>3.04</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AA24" t="n">
         <v>7</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AC24" t="n">
         <v>2.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>6.65</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.51</v>
+        <v>2.29</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="N26" t="n">
-        <v>5.6</v>
+        <v>3.08</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="M27" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="O27" t="n">
         <v>2.32</v>
@@ -3933,10 +3933,10 @@
         <v>3.28</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AA27" t="n">
         <v>3.08</v>
